--- a/public/docs/datas/amiibos.xlsx
+++ b/public/docs/datas/amiibos.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6EF18B-A187-4467-94F4-6B0D3023210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC62011B-BC17-4136-B8C3-92536EA07F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11556" yWindow="3708" windowWidth="21216" windowHeight="15924" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11556" yWindow="12372" windowWidth="22188" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="villagers" sheetId="1" r:id="rId1"/>
-    <sheet name="cars" sheetId="2" r:id="rId2"/>
-    <sheet name="sanrio" sheetId="3" r:id="rId3"/>
+    <sheet name="items" sheetId="4" r:id="rId1"/>
+    <sheet name="villagers" sheetId="1" r:id="rId2"/>
+    <sheet name="cars" sheetId="2" r:id="rId3"/>
+    <sheet name="sanrio" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">cars!$B$1:$B$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">villagers!$B$1:$C$449</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">cars!$B$1:$B$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">villagers!$B$1:$C$449</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="1557">
   <si>
     <t>402_Timmy &amp; Tommy.png</t>
   </si>
@@ -2847,13 +2848,1890 @@
   <si>
     <t>[AC] XS6 - Toby.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>img</t>
+  </si>
+  <si>
+    <t>game</t>
+  </si>
+  <si>
+    <t>series</t>
+  </si>
+  <si>
+    <t>傅达</t>
+  </si>
+  <si>
+    <t>集合啦！动物森友会</t>
+  </si>
+  <si>
+    <t>动物森友会</t>
+  </si>
+  <si>
+    <t>傅珂</t>
+  </si>
+  <si>
+    <t>AC_Celeste.png</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AC_Cyrrus.png</t>
+  </si>
+  <si>
+    <t>AC_Digby.png</t>
+  </si>
+  <si>
+    <t>西施惠 夏装</t>
+  </si>
+  <si>
+    <t>AC_Isabelle (Summer Outfit).png</t>
+  </si>
+  <si>
+    <t>西施惠 冬装</t>
+  </si>
+  <si>
+    <t>AC_Isabelle.png</t>
+  </si>
+  <si>
+    <t>AC_K.K. Slider.png</t>
+  </si>
+  <si>
+    <t>AC_Kappn.png</t>
+  </si>
+  <si>
+    <t>AC_Kicks.png</t>
+  </si>
+  <si>
+    <t>AC_Lottie.png</t>
+  </si>
+  <si>
+    <t>AC_Mabel.png</t>
+  </si>
+  <si>
+    <t>AC_Reese.png</t>
+  </si>
+  <si>
+    <t>AC_Resetti.png</t>
+  </si>
+  <si>
+    <t>AC_Rover.png</t>
+  </si>
+  <si>
+    <t>AC_Timmy &amp; Tommy.png</t>
+  </si>
+  <si>
+    <t>AC_Tom Nook.png</t>
+  </si>
+  <si>
+    <t>Qbby</t>
+  </si>
+  <si>
+    <t>BB_BoxBoy.jpg</t>
+  </si>
+  <si>
+    <t>盒子男孩</t>
+  </si>
+  <si>
+    <t>CR_Chibi Robo.png</t>
+  </si>
+  <si>
+    <t>Chibi-Robo!</t>
+  </si>
+  <si>
+    <t>Diablo3_Loot Goblin.png</t>
+  </si>
+  <si>
+    <t>暗黑破坏神3</t>
+  </si>
+  <si>
+    <t>暗黑破坏神</t>
+  </si>
+  <si>
+    <t>咚奇刚与宝琳</t>
+  </si>
+  <si>
+    <t>DK_咚奇刚与波琳.jpg</t>
+  </si>
+  <si>
+    <t>咚奇刚 蕉力全开</t>
+  </si>
+  <si>
+    <t>咚奇刚</t>
+  </si>
+  <si>
+    <t>名侦探皮卡丘</t>
+  </si>
+  <si>
+    <t>DP_名侦探皮卡丘.jpg</t>
+  </si>
+  <si>
+    <t>宝可梦</t>
+  </si>
+  <si>
+    <t>太阳骑士索拉尔</t>
+  </si>
+  <si>
+    <t>DS_太阳骑士索拉尔.jpg</t>
+  </si>
+  <si>
+    <t>黑暗之魂</t>
+  </si>
+  <si>
+    <t>赛莉卡</t>
+  </si>
+  <si>
+    <t>FE_Celica.jpg</t>
+  </si>
+  <si>
+    <t>火焰纹章</t>
+  </si>
+  <si>
+    <t>阿鲁姆</t>
+  </si>
+  <si>
+    <t>FE_Alm.jpg</t>
+  </si>
+  <si>
+    <t>库洛姆</t>
+  </si>
+  <si>
+    <t>FE_Chrom.jpg</t>
+  </si>
+  <si>
+    <t>琪姬</t>
+  </si>
+  <si>
+    <t>FE_Tiki.jpg</t>
+  </si>
+  <si>
+    <t>帝帝帝大王</t>
+  </si>
+  <si>
+    <t>Kirby_King Dedede.jpg</t>
+  </si>
+  <si>
+    <t>星之卡比</t>
+  </si>
+  <si>
+    <t>卡比</t>
+  </si>
+  <si>
+    <t>Kirby_Kirby.jpg</t>
+  </si>
+  <si>
+    <t>魅塔骑士</t>
+  </si>
+  <si>
+    <t>Kirby_Meta Knight.jpg</t>
+  </si>
+  <si>
+    <t>瓦豆鲁迪</t>
+  </si>
+  <si>
+    <t>Kirby_Waddle Dee.jpg</t>
+  </si>
+  <si>
+    <t>Metroid_萨姆斯·阿兰.jpg</t>
+  </si>
+  <si>
+    <t>密特罗德</t>
+  </si>
+  <si>
+    <t>MD_E.M.M.I..jpg</t>
+  </si>
+  <si>
+    <t>MD_生存恐惧萨姆斯.jpg</t>
+  </si>
+  <si>
+    <t>Metroid_密特罗德.jpg</t>
+  </si>
+  <si>
+    <t>随从艾露猫</t>
+  </si>
+  <si>
+    <t>MHR_随从艾露猫.jpg</t>
+  </si>
+  <si>
+    <t>怪物猎人</t>
+  </si>
+  <si>
+    <t>随从牙猎犬</t>
+  </si>
+  <si>
+    <t>MHR_随从牙猎犬.jpg</t>
+  </si>
+  <si>
+    <t>怨虎龙</t>
+  </si>
+  <si>
+    <t>MHR_怨虎龙.jpg</t>
+  </si>
+  <si>
+    <t>爵银龙猫</t>
+  </si>
+  <si>
+    <t>MHRS_爵银龙猫.jpg</t>
+  </si>
+  <si>
+    <t>爵银龙犬</t>
+  </si>
+  <si>
+    <t>MHRS_爵银龙犬.jpg</t>
+  </si>
+  <si>
+    <t>爵银龙</t>
+  </si>
+  <si>
+    <t>MHRS_爵银龙.jpg</t>
+  </si>
+  <si>
+    <t>MHST_冰牙龙与亚尤利娅.jpg</t>
+  </si>
+  <si>
+    <t>MHST_彩鸟与丹前辈.jpg</t>
+  </si>
+  <si>
+    <t>MHST_雌火龙与修瓦尔.jpg</t>
+  </si>
+  <si>
+    <t>MHST_独眼雄火龙与男骑士.jpg</t>
+  </si>
+  <si>
+    <t>MHST_独眼雄火龙与女骑士.jpg</t>
+  </si>
+  <si>
+    <t>MHST_纳比尔.jpg</t>
+  </si>
+  <si>
+    <t>MHST2_艾娜.jpg</t>
+  </si>
+  <si>
+    <t>MHST2_毁灭火龙.jpg</t>
+  </si>
+  <si>
+    <t>MHST2_月露.jpg</t>
+  </si>
+  <si>
+    <t>MM_洛克人.jpg</t>
+  </si>
+  <si>
+    <t>洛克人</t>
+  </si>
+  <si>
+    <t>Pikmin_皮克敏.jpg</t>
+  </si>
+  <si>
+    <t>皮克敏</t>
+  </si>
+  <si>
+    <t>卢克</t>
+  </si>
+  <si>
+    <t>SF6_卢克.jpg</t>
+  </si>
+  <si>
+    <t>街头霸王</t>
+  </si>
+  <si>
+    <t>杰米</t>
+  </si>
+  <si>
+    <t>SF6_杰米.jpg</t>
+  </si>
+  <si>
+    <t>金柏莉</t>
+  </si>
+  <si>
+    <t>SF6_金柏莉.jpg</t>
+  </si>
+  <si>
+    <t>Sky_Donkey Kong.png</t>
+  </si>
+  <si>
+    <t>Sky_Dark Donkey Kong.png</t>
+  </si>
+  <si>
+    <t>Sky_Bowser.png</t>
+  </si>
+  <si>
+    <t>Sky_Dark Bowser.png</t>
+  </si>
+  <si>
+    <t>马力欧</t>
+  </si>
+  <si>
+    <t>SM_Mario.png</t>
+  </si>
+  <si>
+    <t>马力欧 银色</t>
+  </si>
+  <si>
+    <t>SM_Mario - Silver.png</t>
+  </si>
+  <si>
+    <t>马力欧 金色</t>
+  </si>
+  <si>
+    <t>SM_Mario - Gold.png</t>
+  </si>
+  <si>
+    <t>马力欧 经典色</t>
+  </si>
+  <si>
+    <t>SM_Mario Classic Color.png</t>
+  </si>
+  <si>
+    <t>马力欧 现代色</t>
+  </si>
+  <si>
+    <t>SM_Mario Modern Color.png</t>
+  </si>
+  <si>
+    <t>路易吉</t>
+  </si>
+  <si>
+    <t>SM_Luigi.jpg</t>
+  </si>
+  <si>
+    <t>猫咪马力欧</t>
+  </si>
+  <si>
+    <t>SM_Cat Mario.jpg</t>
+  </si>
+  <si>
+    <t>碧姬公主</t>
+  </si>
+  <si>
+    <t>SM_Peach.jpg</t>
+  </si>
+  <si>
+    <t>猫咪碧姬公主</t>
+  </si>
+  <si>
+    <t>SM_Cat Peach.jpg</t>
+  </si>
+  <si>
+    <t>罗洁塔</t>
+  </si>
+  <si>
+    <t>SM_Rosalina.jpg</t>
+  </si>
+  <si>
+    <t>奇诺比奥</t>
+  </si>
+  <si>
+    <t>SM_Toad.png</t>
+  </si>
+  <si>
+    <t>黛西公主</t>
+  </si>
+  <si>
+    <t>SM_Daisy.jpg</t>
+  </si>
+  <si>
+    <t>SM_Donkey Kong.jpg</t>
+  </si>
+  <si>
+    <t>迪迪</t>
+  </si>
+  <si>
+    <t>SM_Diddy Kong.png</t>
+  </si>
+  <si>
+    <t>酷霸王</t>
+  </si>
+  <si>
+    <t>SM_Bowser.png</t>
+  </si>
+  <si>
+    <t>栗宝宝</t>
+  </si>
+  <si>
+    <t>SM_Goomba.jpg</t>
+  </si>
+  <si>
+    <t>慢慢龟</t>
+  </si>
+  <si>
+    <t>SM_Koopa Troopa.jpg</t>
+  </si>
+  <si>
+    <t>害羞幽灵</t>
+  </si>
+  <si>
+    <t>SM_Boo.jpg</t>
+  </si>
+  <si>
+    <t>瓦力欧</t>
+  </si>
+  <si>
+    <t>SM_Wario.jpg</t>
+  </si>
+  <si>
+    <t>瓦路易吉</t>
+  </si>
+  <si>
+    <t>SM_Waluigi.jpg</t>
+  </si>
+  <si>
+    <t>耀西</t>
+  </si>
+  <si>
+    <t>SM_Yoshi.png</t>
+  </si>
+  <si>
+    <t>SMO_Mario - Wedding.jpg</t>
+  </si>
+  <si>
+    <t>SMO_Peach - Wedding.png</t>
+  </si>
+  <si>
+    <t>SMO_Bowser.jpg</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight.png</t>
+  </si>
+  <si>
+    <t>铲子骑士</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight (Gold Edition).png</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight NEW.png</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight Unlocked.png</t>
+  </si>
+  <si>
+    <t>SN_Plague Knight.png</t>
+  </si>
+  <si>
+    <t>SN_King Knight.png</t>
+  </si>
+  <si>
+    <t>SN_Specter Knight.png</t>
+  </si>
+  <si>
+    <t>Splatoon_麻辣鱿物小拟.jpg</t>
+  </si>
+  <si>
+    <t>喷射战士</t>
+  </si>
+  <si>
+    <t>Splatoon_麻辣鱿物小萤.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族男孩(紫色).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族男孩.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族女孩(青柠绿).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族女孩.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族乌贼(橙色).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族乌贼.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_腕儿姐妹饭田.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_腕儿姐妹小姬.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_鱿鱼族男孩.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_鱿鱼族女孩.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_鱿鱼族乌贼.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_章鱼圈男孩.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_章鱼圈女孩.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon2_章鱼圈章鱼.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_麻辣鱿物小拟(幻界).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_麻辣鱿物小萤(幻界).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_腕儿姐妹饭田(秩序篇).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_腕儿姐妹小姬(秩序篇).jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_小鲑鱼.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱿鱼族.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱼浆帮鬼福.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱼浆帮曼曼.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱼浆帮莎莎.jpg</t>
+  </si>
+  <si>
+    <t>Splatoon3_章鱼圈.jpg</t>
+  </si>
+  <si>
+    <t>SSB_AC_Isabelle.jpg</t>
+  </si>
+  <si>
+    <t>任天堂大乱斗</t>
+  </si>
+  <si>
+    <t>SSB_AC_Villager.jpg</t>
+  </si>
+  <si>
+    <t>SSB_BJ_Bayonetta.jpg</t>
+  </si>
+  <si>
+    <t>贝优妮塔</t>
+  </si>
+  <si>
+    <t>SSB_BJ_Bayonetta P2.jpg</t>
+  </si>
+  <si>
+    <t>SSB_BK_Banjo &amp; Kazooie.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Castle_Simon.jpg</t>
+  </si>
+  <si>
+    <t>恶魔城</t>
+  </si>
+  <si>
+    <t>SSB_Castle_Richter.jpg</t>
+  </si>
+  <si>
+    <t>SSB_DK_Donkey Kong.jpg</t>
+  </si>
+  <si>
+    <t>SSB_DK_Diddy Kong.jpg</t>
+  </si>
+  <si>
+    <t>SSB_DK_King K. Rool.png</t>
+  </si>
+  <si>
+    <t>SSB_Duck Hunt Duo.jpg</t>
+  </si>
+  <si>
+    <t>SSB_DM_Dr Mario.jpg</t>
+  </si>
+  <si>
+    <t>勇者</t>
+  </si>
+  <si>
+    <t>SSB_DQ_Hero.jpg</t>
+  </si>
+  <si>
+    <t>勇者斗恶龙</t>
+  </si>
+  <si>
+    <t>SSB_FE_Chrom.jpg</t>
+  </si>
+  <si>
+    <t>卡姆依</t>
+  </si>
+  <si>
+    <t>SSB_FE_Corrin P1.jpg</t>
+  </si>
+  <si>
+    <t>SSB_FE_Corrin P2.jpg</t>
+  </si>
+  <si>
+    <t>艾克</t>
+  </si>
+  <si>
+    <t>SSB_FE_Ike.jpg</t>
+  </si>
+  <si>
+    <t>露琪亚</t>
+  </si>
+  <si>
+    <t>SSB_FE_Lucina.jpg</t>
+  </si>
+  <si>
+    <t>马尔斯</t>
+  </si>
+  <si>
+    <t>SSB_FE_Marth.jpg</t>
+  </si>
+  <si>
+    <t>帕鲁迪娜</t>
+  </si>
+  <si>
+    <t>SSB_FE_Palutena.jpg</t>
+  </si>
+  <si>
+    <t>鲁弗莱</t>
+  </si>
+  <si>
+    <t>SSB_FE_Robin.jpg</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+  </si>
+  <si>
+    <t>SSB_FE_Roy.jpg</t>
+  </si>
+  <si>
+    <t>贝雷特</t>
+  </si>
+  <si>
+    <t>SSB_FE_Byleth.jpg</t>
+  </si>
+  <si>
+    <t>克劳德</t>
+  </si>
+  <si>
+    <t>SSB_FF_Cloud.jpg</t>
+  </si>
+  <si>
+    <t>最终幻想</t>
+  </si>
+  <si>
+    <t>SSB_FF_Cloud P2.jpg</t>
+  </si>
+  <si>
+    <t>萨菲罗斯</t>
+  </si>
+  <si>
+    <t>SSB_FF_Sephiroth.jpg</t>
+  </si>
+  <si>
+    <t>SSB_FZ_Captain Falcon.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Ice Climbers.png</t>
+  </si>
+  <si>
+    <t>SSB_KH_Sora.jpg</t>
+  </si>
+  <si>
+    <t>王国之心</t>
+  </si>
+  <si>
+    <t>SSB_KI_Pit.jpg</t>
+  </si>
+  <si>
+    <t>光之神话</t>
+  </si>
+  <si>
+    <t>SSB_KI_Dark Pit.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Kirby_Kirby.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Kirby_Meta Knight.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Kirby_King Dedede.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MC_Steve.png</t>
+  </si>
+  <si>
+    <t>我的世界</t>
+  </si>
+  <si>
+    <t>SSB_MC_Alex.png</t>
+  </si>
+  <si>
+    <t>SSB_MD_黑暗萨姆斯.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MD_利德雷.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MD_零装甲萨姆斯.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MD_萨姆斯.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MG_Snake.png</t>
+  </si>
+  <si>
+    <t>合金装备</t>
+  </si>
+  <si>
+    <t>SSB_Mii Swordsman.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Mii Fighter.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Mii Gunner.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Min Min.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MM_Mega Man.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MM_Mega Man (Gold Edition).jpg</t>
+  </si>
+  <si>
+    <t>SSB_Mother_Ness.jpg</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>SSB_Mother_Lucas.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Mr GAME &amp; WATCH.jpg</t>
+  </si>
+  <si>
+    <t>SSB_MT_Little Mac.jpg</t>
+  </si>
+  <si>
+    <t>SSB_P5_Joker.jpg</t>
+  </si>
+  <si>
+    <t>Persona 5</t>
+  </si>
+  <si>
+    <t>SSB_Pac Man.jpg</t>
+  </si>
+  <si>
+    <t>吃豆人</t>
+  </si>
+  <si>
+    <t>SSB_Pikmin_Oilmar.jpg</t>
+  </si>
+  <si>
+    <t>训练家</t>
+  </si>
+  <si>
+    <t>SSB_PM_Pokémon Trainer.jpg</t>
+  </si>
+  <si>
+    <t>杰尼龟</t>
+  </si>
+  <si>
+    <t>SSB_PM_Squirtle.png</t>
+  </si>
+  <si>
+    <t>妙蛙花</t>
+  </si>
+  <si>
+    <t>SSB_PM_Ivysaur.png</t>
+  </si>
+  <si>
+    <t>喷火龙</t>
+  </si>
+  <si>
+    <t>SSB_PM_Charizard.jpg</t>
+  </si>
+  <si>
+    <t>皮丘</t>
+  </si>
+  <si>
+    <t>SSB_PM_Pichu.jpg</t>
+  </si>
+  <si>
+    <t>皮卡超</t>
+  </si>
+  <si>
+    <t>SSB_PM_Pikachu.jpg</t>
+  </si>
+  <si>
+    <t>甲贺忍蛙</t>
+  </si>
+  <si>
+    <t>SSB_PM_Greninja.jpg</t>
+  </si>
+  <si>
+    <t>炽焰咆啸虎</t>
+  </si>
+  <si>
+    <t>SSB_PM_Incineroar.jpg</t>
+  </si>
+  <si>
+    <t>胖丁</t>
+  </si>
+  <si>
+    <t>SSB_PM_Jigglypuff.jpg</t>
+  </si>
+  <si>
+    <t>卢卡利欧</t>
+  </si>
+  <si>
+    <t>SSB_PM_Lucario.jpg</t>
+  </si>
+  <si>
+    <t>超梦</t>
+  </si>
+  <si>
+    <t>SSB_PM_Mewtwo.jpg</t>
+  </si>
+  <si>
+    <t>SSB_ROB NES.jpg</t>
+  </si>
+  <si>
+    <t>SSB_ROB Famicom Edition.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SF_Fox.jpg</t>
+  </si>
+  <si>
+    <t>星际火狐</t>
+  </si>
+  <si>
+    <t>SSB_SF_Falco.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SF_Wolf.png</t>
+  </si>
+  <si>
+    <t>SSB_SF_Terry.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SF_Kazuya.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SF_Ken.png</t>
+  </si>
+  <si>
+    <t>SSB_SF_Ryu.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SM_Mario.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SM_Luigi.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SM_Peach.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SM_Rosalina.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SM_Daisy.png</t>
+  </si>
+  <si>
+    <t>SSB_SM_Yoshi.jpg</t>
+  </si>
+  <si>
+    <t>SSB_SM_Bowser.jpg</t>
+  </si>
+  <si>
+    <t>小酷霸</t>
+  </si>
+  <si>
+    <t>SSB_SM_Bowser Jr..jpg</t>
+  </si>
+  <si>
+    <t>吞食花</t>
+  </si>
+  <si>
+    <t>SSB_SM_Piranha Plant.png</t>
+  </si>
+  <si>
+    <t>SSB_SM_Wario.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Sonic.jpg</t>
+  </si>
+  <si>
+    <t>索尼克</t>
+  </si>
+  <si>
+    <t>SSB_Splatoon_Inkling Girl.png</t>
+  </si>
+  <si>
+    <t>SSB_Wii Fit Trainer.jpg</t>
+  </si>
+  <si>
+    <t>修尔克</t>
+  </si>
+  <si>
+    <t>SSB_XC_Shulk.jpg</t>
+  </si>
+  <si>
+    <t>异度神剑</t>
+  </si>
+  <si>
+    <t>光</t>
+  </si>
+  <si>
+    <t>SSB_XC_Mythra.jpg</t>
+  </si>
+  <si>
+    <t>焰</t>
+  </si>
+  <si>
+    <t>SSB_XC_Pyra.jpg</t>
+  </si>
+  <si>
+    <t>林克</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Link.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Toon Link.jpg</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Young Link.png</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Zelda.jpg</t>
+  </si>
+  <si>
+    <t>希克</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Sheik.jpg</t>
+  </si>
+  <si>
+    <t>加侬多夫</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Ganondorf.jpg</t>
+  </si>
+  <si>
+    <t>诺亚</t>
+  </si>
+  <si>
+    <t>XC3_诺亚.jpg</t>
+  </si>
+  <si>
+    <t>异度神剑3</t>
+  </si>
+  <si>
+    <t>弥央</t>
+  </si>
+  <si>
+    <t>XC3_弥央.jpg</t>
+  </si>
+  <si>
+    <t>Yoshi_Blue Yoshi.png</t>
+  </si>
+  <si>
+    <t>毛线耀西</t>
+  </si>
+  <si>
+    <t>Yoshi_Green Yoshi.png</t>
+  </si>
+  <si>
+    <t>Yoshi_Pink Yoshi.png</t>
+  </si>
+  <si>
+    <t>Yoshi_Mega Yoshi.png</t>
+  </si>
+  <si>
+    <t>Yoshi_毛线波奇.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_初始林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 30周年</t>
+  </si>
+  <si>
+    <t>Zelda_风之杖卡通林克.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_风之杖塞尔达.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_时之笛林克.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_魔吉拉的面具林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 魔吉拉的面具</t>
+  </si>
+  <si>
+    <t>Zelda_黄昏公主林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 黄昏公主</t>
+  </si>
+  <si>
+    <t>Zelda_黄昏公主野狼林克.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_御天之剑林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 御天之剑</t>
+  </si>
+  <si>
+    <t>Zelda_御天之剑塞尔达与洛夫特飞鸟.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息骑士林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 旷野之息</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息射手林克.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息塞尔达.jpg</t>
+  </si>
+  <si>
+    <t>力巴尔</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息力巴尔.jpg</t>
+  </si>
+  <si>
+    <t>米法</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息米法.jpg</t>
+  </si>
+  <si>
+    <t>乌尔波扎</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息乌尔波扎.jpg</t>
+  </si>
+  <si>
+    <t>达尔克尔</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息达尔克尔.jpg</t>
+  </si>
+  <si>
+    <t>守护者</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息守护者.jpg</t>
+  </si>
+  <si>
+    <t>波克布林</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息波克布林.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_织梦岛林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 织梦岛</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪林克.jpg</t>
+  </si>
+  <si>
+    <t>塞尔达 王国之泪</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪塞尔达.jpg</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪加侬多夫.jpg</t>
+  </si>
+  <si>
+    <t>丘栗</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪丘栗.jpg</t>
+  </si>
+  <si>
+    <t>希多</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪希多.jpg</t>
+  </si>
+  <si>
+    <t>露珠</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪露珠.jpg</t>
+  </si>
+  <si>
+    <t>阿沅</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪阿沅.jpg</t>
+  </si>
+  <si>
+    <t>code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC_Blathers.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC_Blathers</t>
+  </si>
+  <si>
+    <t>AC_Celeste</t>
+  </si>
+  <si>
+    <t>AC_Cyrrus</t>
+  </si>
+  <si>
+    <t>AC_Digby</t>
+  </si>
+  <si>
+    <t>AC_Isabelle (Summer Outfit)</t>
+  </si>
+  <si>
+    <t>AC_Isabelle</t>
+  </si>
+  <si>
+    <t>AC_K.K. Slider</t>
+  </si>
+  <si>
+    <t>AC_Kappn</t>
+  </si>
+  <si>
+    <t>AC_Kicks</t>
+  </si>
+  <si>
+    <t>AC_Lottie</t>
+  </si>
+  <si>
+    <t>AC_Mabel</t>
+  </si>
+  <si>
+    <t>AC_Reese</t>
+  </si>
+  <si>
+    <t>AC_Resetti</t>
+  </si>
+  <si>
+    <t>AC_Rover</t>
+  </si>
+  <si>
+    <t>AC_Timmy &amp; Tommy</t>
+  </si>
+  <si>
+    <t>AC_Tom Nook</t>
+  </si>
+  <si>
+    <t>BB_BoxBoy</t>
+  </si>
+  <si>
+    <t>CR_Chibi Robo</t>
+  </si>
+  <si>
+    <t>Diablo3_Loot Goblin</t>
+  </si>
+  <si>
+    <t>DK_咚奇刚与波琳</t>
+  </si>
+  <si>
+    <t>DP_名侦探皮卡丘</t>
+  </si>
+  <si>
+    <t>DS_太阳骑士索拉尔</t>
+  </si>
+  <si>
+    <t>FE_Celica</t>
+  </si>
+  <si>
+    <t>FE_Alm</t>
+  </si>
+  <si>
+    <t>FE_Chrom</t>
+  </si>
+  <si>
+    <t>FE_Tiki</t>
+  </si>
+  <si>
+    <t>Kirby_King Dedede</t>
+  </si>
+  <si>
+    <t>Kirby_Kirby</t>
+  </si>
+  <si>
+    <t>Kirby_Meta Knight</t>
+  </si>
+  <si>
+    <t>Kirby_Waddle Dee</t>
+  </si>
+  <si>
+    <t>Metroid_萨姆斯·阿兰</t>
+  </si>
+  <si>
+    <t>MD_E.M.M.I.</t>
+  </si>
+  <si>
+    <t>MD_生存恐惧萨姆斯</t>
+  </si>
+  <si>
+    <t>Metroid_密特罗德</t>
+  </si>
+  <si>
+    <t>MHR_随从艾露猫</t>
+  </si>
+  <si>
+    <t>MHR_随从牙猎犬</t>
+  </si>
+  <si>
+    <t>MHR_怨虎龙</t>
+  </si>
+  <si>
+    <t>MHRS_爵银龙猫</t>
+  </si>
+  <si>
+    <t>MHRS_爵银龙犬</t>
+  </si>
+  <si>
+    <t>MHRS_爵银龙</t>
+  </si>
+  <si>
+    <t>MHST_冰牙龙与亚尤利娅</t>
+  </si>
+  <si>
+    <t>MHST_彩鸟与丹前辈</t>
+  </si>
+  <si>
+    <t>MHST_雌火龙与修瓦尔</t>
+  </si>
+  <si>
+    <t>MHST_独眼雄火龙与男骑士</t>
+  </si>
+  <si>
+    <t>MHST_独眼雄火龙与女骑士</t>
+  </si>
+  <si>
+    <t>MHST_纳比尔</t>
+  </si>
+  <si>
+    <t>MHST2_艾娜</t>
+  </si>
+  <si>
+    <t>MHST2_毁灭火龙</t>
+  </si>
+  <si>
+    <t>MHST2_月露</t>
+  </si>
+  <si>
+    <t>MM_洛克人</t>
+  </si>
+  <si>
+    <t>Pikmin_皮克敏</t>
+  </si>
+  <si>
+    <t>SF6_卢克</t>
+  </si>
+  <si>
+    <t>SF6_杰米</t>
+  </si>
+  <si>
+    <t>SF6_金柏莉</t>
+  </si>
+  <si>
+    <t>Sky_Donkey Kong</t>
+  </si>
+  <si>
+    <t>Sky_Dark Donkey Kong</t>
+  </si>
+  <si>
+    <t>Sky_Bowser</t>
+  </si>
+  <si>
+    <t>Sky_Dark Bowser</t>
+  </si>
+  <si>
+    <t>SM_Mario</t>
+  </si>
+  <si>
+    <t>SM_Mario - Silver</t>
+  </si>
+  <si>
+    <t>SM_Mario - Gold</t>
+  </si>
+  <si>
+    <t>SM_Mario Classic Color</t>
+  </si>
+  <si>
+    <t>SM_Mario Modern Color</t>
+  </si>
+  <si>
+    <t>SM_Luigi</t>
+  </si>
+  <si>
+    <t>SM_Cat Mario</t>
+  </si>
+  <si>
+    <t>SM_Peach</t>
+  </si>
+  <si>
+    <t>SM_Cat Peach</t>
+  </si>
+  <si>
+    <t>SM_Rosalina</t>
+  </si>
+  <si>
+    <t>SM_Toad</t>
+  </si>
+  <si>
+    <t>SM_Daisy</t>
+  </si>
+  <si>
+    <t>SM_Donkey Kong</t>
+  </si>
+  <si>
+    <t>SM_Diddy Kong</t>
+  </si>
+  <si>
+    <t>SM_Bowser</t>
+  </si>
+  <si>
+    <t>SM_Goomba</t>
+  </si>
+  <si>
+    <t>SM_Koopa Troopa</t>
+  </si>
+  <si>
+    <t>SM_Boo</t>
+  </si>
+  <si>
+    <t>SM_Wario</t>
+  </si>
+  <si>
+    <t>SM_Waluigi</t>
+  </si>
+  <si>
+    <t>SM_Yoshi</t>
+  </si>
+  <si>
+    <t>SMO_Mario - Wedding</t>
+  </si>
+  <si>
+    <t>SMO_Peach - Wedding</t>
+  </si>
+  <si>
+    <t>SMO_Bowser</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight (Gold Edition)</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight NEW</t>
+  </si>
+  <si>
+    <t>SN_Shovel Knight Unlocked</t>
+  </si>
+  <si>
+    <t>SN_Plague Knight</t>
+  </si>
+  <si>
+    <t>SN_King Knight</t>
+  </si>
+  <si>
+    <t>SN_Specter Knight</t>
+  </si>
+  <si>
+    <t>Splatoon_麻辣鱿物小拟</t>
+  </si>
+  <si>
+    <t>Splatoon_麻辣鱿物小萤</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族男孩(紫色)</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族男孩</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族女孩(青柠绿)</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族女孩</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族乌贼(橙色)</t>
+  </si>
+  <si>
+    <t>Splatoon_鱿鱼族乌贼</t>
+  </si>
+  <si>
+    <t>Splatoon2_腕儿姐妹饭田</t>
+  </si>
+  <si>
+    <t>Splatoon2_腕儿姐妹小姬</t>
+  </si>
+  <si>
+    <t>Splatoon2_鱿鱼族男孩</t>
+  </si>
+  <si>
+    <t>Splatoon2_鱿鱼族女孩</t>
+  </si>
+  <si>
+    <t>Splatoon2_鱿鱼族乌贼</t>
+  </si>
+  <si>
+    <t>Splatoon2_章鱼圈男孩</t>
+  </si>
+  <si>
+    <t>Splatoon2_章鱼圈女孩</t>
+  </si>
+  <si>
+    <t>Splatoon2_章鱼圈章鱼</t>
+  </si>
+  <si>
+    <t>Splatoon3_麻辣鱿物小拟(幻界)</t>
+  </si>
+  <si>
+    <t>Splatoon3_麻辣鱿物小萤(幻界)</t>
+  </si>
+  <si>
+    <t>Splatoon3_腕儿姐妹饭田(秩序篇)</t>
+  </si>
+  <si>
+    <t>Splatoon3_腕儿姐妹小姬(秩序篇)</t>
+  </si>
+  <si>
+    <t>Splatoon3_小鲑鱼</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱿鱼族</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱼浆帮鬼福</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱼浆帮曼曼</t>
+  </si>
+  <si>
+    <t>Splatoon3_鱼浆帮莎莎</t>
+  </si>
+  <si>
+    <t>Splatoon3_章鱼圈</t>
+  </si>
+  <si>
+    <t>SSB_AC_Isabelle</t>
+  </si>
+  <si>
+    <t>SSB_AC_Villager</t>
+  </si>
+  <si>
+    <t>SSB_BJ_Bayonetta</t>
+  </si>
+  <si>
+    <t>SSB_BJ_Bayonetta P2</t>
+  </si>
+  <si>
+    <t>SSB_BK_Banjo &amp; Kazooie</t>
+  </si>
+  <si>
+    <t>SSB_Castle_Simon</t>
+  </si>
+  <si>
+    <t>SSB_Castle_Richter</t>
+  </si>
+  <si>
+    <t>SSB_DK_Donkey Kong</t>
+  </si>
+  <si>
+    <t>SSB_DK_Diddy Kong</t>
+  </si>
+  <si>
+    <t>SSB_DK_King K. Rool</t>
+  </si>
+  <si>
+    <t>SSB_Duck Hunt Duo</t>
+  </si>
+  <si>
+    <t>SSB_DM_Dr Mario</t>
+  </si>
+  <si>
+    <t>SSB_DQ_Hero</t>
+  </si>
+  <si>
+    <t>SSB_FE_Chrom</t>
+  </si>
+  <si>
+    <t>SSB_FE_Corrin P1</t>
+  </si>
+  <si>
+    <t>SSB_FE_Corrin P2</t>
+  </si>
+  <si>
+    <t>SSB_FE_Ike</t>
+  </si>
+  <si>
+    <t>SSB_FE_Lucina</t>
+  </si>
+  <si>
+    <t>SSB_FE_Marth</t>
+  </si>
+  <si>
+    <t>SSB_FE_Palutena</t>
+  </si>
+  <si>
+    <t>SSB_FE_Robin</t>
+  </si>
+  <si>
+    <t>SSB_FE_Roy</t>
+  </si>
+  <si>
+    <t>SSB_FE_Byleth</t>
+  </si>
+  <si>
+    <t>SSB_FF_Cloud</t>
+  </si>
+  <si>
+    <t>SSB_FF_Cloud P2</t>
+  </si>
+  <si>
+    <t>SSB_FF_Sephiroth</t>
+  </si>
+  <si>
+    <t>SSB_FZ_Captain Falcon</t>
+  </si>
+  <si>
+    <t>SSB_Ice Climbers</t>
+  </si>
+  <si>
+    <t>SSB_KH_Sora</t>
+  </si>
+  <si>
+    <t>SSB_KI_Pit</t>
+  </si>
+  <si>
+    <t>SSB_KI_Dark Pit</t>
+  </si>
+  <si>
+    <t>SSB_Kirby_Kirby</t>
+  </si>
+  <si>
+    <t>SSB_Kirby_Meta Knight</t>
+  </si>
+  <si>
+    <t>SSB_Kirby_King Dedede</t>
+  </si>
+  <si>
+    <t>SSB_MC_Steve</t>
+  </si>
+  <si>
+    <t>SSB_MC_Alex</t>
+  </si>
+  <si>
+    <t>SSB_MD_黑暗萨姆斯</t>
+  </si>
+  <si>
+    <t>SSB_MD_利德雷</t>
+  </si>
+  <si>
+    <t>SSB_MD_零装甲萨姆斯</t>
+  </si>
+  <si>
+    <t>SSB_MD_萨姆斯</t>
+  </si>
+  <si>
+    <t>SSB_MG_Snake</t>
+  </si>
+  <si>
+    <t>SSB_Mii Swordsman</t>
+  </si>
+  <si>
+    <t>SSB_Mii Fighter</t>
+  </si>
+  <si>
+    <t>SSB_Mii Gunner</t>
+  </si>
+  <si>
+    <t>SSB_Min Min</t>
+  </si>
+  <si>
+    <t>SSB_MM_Mega Man</t>
+  </si>
+  <si>
+    <t>SSB_MM_Mega Man (Gold Edition)</t>
+  </si>
+  <si>
+    <t>SSB_Mother_Ness</t>
+  </si>
+  <si>
+    <t>SSB_Mother_Lucas</t>
+  </si>
+  <si>
+    <t>SSB_Mr GAME &amp; WATCH</t>
+  </si>
+  <si>
+    <t>SSB_MT_Little Mac</t>
+  </si>
+  <si>
+    <t>SSB_P5_Joker</t>
+  </si>
+  <si>
+    <t>SSB_Pac Man</t>
+  </si>
+  <si>
+    <t>SSB_Pikmin_Oilmar</t>
+  </si>
+  <si>
+    <t>SSB_PM_Pokémon Trainer</t>
+  </si>
+  <si>
+    <t>SSB_PM_Squirtle</t>
+  </si>
+  <si>
+    <t>SSB_PM_Ivysaur</t>
+  </si>
+  <si>
+    <t>SSB_PM_Charizard</t>
+  </si>
+  <si>
+    <t>SSB_PM_Pichu</t>
+  </si>
+  <si>
+    <t>SSB_PM_Pikachu</t>
+  </si>
+  <si>
+    <t>SSB_PM_Greninja</t>
+  </si>
+  <si>
+    <t>SSB_PM_Incineroar</t>
+  </si>
+  <si>
+    <t>SSB_PM_Jigglypuff</t>
+  </si>
+  <si>
+    <t>SSB_PM_Lucario</t>
+  </si>
+  <si>
+    <t>SSB_PM_Mewtwo</t>
+  </si>
+  <si>
+    <t>SSB_ROB NES</t>
+  </si>
+  <si>
+    <t>SSB_ROB Famicom Edition</t>
+  </si>
+  <si>
+    <t>SSB_SF_Fox</t>
+  </si>
+  <si>
+    <t>SSB_SF_Falco</t>
+  </si>
+  <si>
+    <t>SSB_SF_Wolf</t>
+  </si>
+  <si>
+    <t>SSB_SF_Terry</t>
+  </si>
+  <si>
+    <t>SSB_SF_Kazuya</t>
+  </si>
+  <si>
+    <t>SSB_SF_Ken</t>
+  </si>
+  <si>
+    <t>SSB_SF_Ryu</t>
+  </si>
+  <si>
+    <t>SSB_SM_Mario</t>
+  </si>
+  <si>
+    <t>SSB_SM_Luigi</t>
+  </si>
+  <si>
+    <t>SSB_SM_Peach</t>
+  </si>
+  <si>
+    <t>SSB_SM_Rosalina</t>
+  </si>
+  <si>
+    <t>SSB_SM_Daisy</t>
+  </si>
+  <si>
+    <t>SSB_SM_Yoshi</t>
+  </si>
+  <si>
+    <t>SSB_SM_Bowser</t>
+  </si>
+  <si>
+    <t>SSB_SM_Bowser Jr.</t>
+  </si>
+  <si>
+    <t>SSB_SM_Piranha Plant</t>
+  </si>
+  <si>
+    <t>SSB_SM_Wario</t>
+  </si>
+  <si>
+    <t>SSB_Sonic</t>
+  </si>
+  <si>
+    <t>SSB_Splatoon_Inkling Girl</t>
+  </si>
+  <si>
+    <t>SSB_Wii Fit Trainer</t>
+  </si>
+  <si>
+    <t>SSB_XC_Shulk</t>
+  </si>
+  <si>
+    <t>SSB_XC_Mythra</t>
+  </si>
+  <si>
+    <t>SSB_XC_Pyra</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Link</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Toon Link</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Young Link</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Zelda</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Sheik</t>
+  </si>
+  <si>
+    <t>SSB_Zelda_Ganondorf</t>
+  </si>
+  <si>
+    <t>XC3_诺亚</t>
+  </si>
+  <si>
+    <t>XC3_弥央</t>
+  </si>
+  <si>
+    <t>Yoshi_Blue Yoshi</t>
+  </si>
+  <si>
+    <t>Yoshi_Green Yoshi</t>
+  </si>
+  <si>
+    <t>Yoshi_Pink Yoshi</t>
+  </si>
+  <si>
+    <t>Yoshi_Mega Yoshi</t>
+  </si>
+  <si>
+    <t>Yoshi_毛线波奇</t>
+  </si>
+  <si>
+    <t>Zelda_初始林克</t>
+  </si>
+  <si>
+    <t>Zelda_风之杖卡通林克</t>
+  </si>
+  <si>
+    <t>Zelda_风之杖塞尔达</t>
+  </si>
+  <si>
+    <t>Zelda_时之笛林克</t>
+  </si>
+  <si>
+    <t>Zelda_魔吉拉的面具林克</t>
+  </si>
+  <si>
+    <t>Zelda_黄昏公主林克</t>
+  </si>
+  <si>
+    <t>Zelda_黄昏公主野狼林克</t>
+  </si>
+  <si>
+    <t>Zelda_御天之剑林克</t>
+  </si>
+  <si>
+    <t>Zelda_御天之剑塞尔达与洛夫特飞鸟</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息骑士林克</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息射手林克</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息塞尔达</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息力巴尔</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息米法</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息乌尔波扎</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息达尔克尔</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息守护者</t>
+  </si>
+  <si>
+    <t>Zelda_旷野之息波克布林</t>
+  </si>
+  <si>
+    <t>Zelda_织梦岛林克</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪林克</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪塞尔达</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪加侬多夫</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪丘栗</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪希多</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪露珠</t>
+  </si>
+  <si>
+    <t>Zelda_王国之泪阿沅</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2874,6 +4752,12 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2899,15 +4783,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{FC8B159E-88F5-4AFA-B5E7-495597B37905}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3184,6 +5071,4190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C3832A-76EC-49EA-B6A3-8416748BF803}">
+  <dimension ref="A1:E245"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A237" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A241" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A243" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C449"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -8136,7 +14207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62CD117-49EC-4ED6-BFF8-B9A329E4B3DE}">
   <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -8558,7 +14629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34153C2-159F-4644-8425-FE12225F265A}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
